--- a/Project 1 Data Quality Assessment/D5 Topological Role Consistency and Structural Representativeness/outputs/audit/support_migration/D5_support_migration_audit.xlsx
+++ b/Project 1 Data Quality Assessment/D5 Topological Role Consistency and Structural Representativeness/outputs/audit/support_migration/D5_support_migration_audit.xlsx
@@ -20,12 +20,12 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'01_monthly_occupancy'!$A$1:$G$15</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'01b_pre_post_shift'!$A$1:$H$5</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'02_template_occupancy_56'!$A$1:$CB$57</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'03_L1_L2_blockers'!$A$1:$CI$15</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'04_L2_L3_blockers'!$A$1:$CN$43</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'05_loss_attribution'!$A$1:$F$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'02_template_occupancy_56'!$A$1:$CD$57</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'03_L1_L2_blockers'!$A$1:$CK$15</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'04_L2_L3_blockers'!$A$1:$CP$43</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'05_loss_attribution'!$A$1:$H$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'06_counterfactual'!$A$1:$E$8</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'07_reference_horizon'!$A$1:$H$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'07_reference_horizon'!$A$1:$I$13</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'08_monthly_eligibility'!$A$1:$F$10</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1085,7 +1085,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB57"/>
+  <dimension ref="A1:CD57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -1162,12 +1162,14 @@
     <col width="22" customWidth="1" min="72" max="72"/>
     <col width="23" customWidth="1" min="73" max="73"/>
     <col width="23" customWidth="1" min="74" max="74"/>
-    <col width="11" customWidth="1" min="75" max="75"/>
-    <col width="21" customWidth="1" min="76" max="76"/>
+    <col width="23" customWidth="1" min="75" max="75"/>
+    <col width="11" customWidth="1" min="76" max="76"/>
     <col width="21" customWidth="1" min="77" max="77"/>
     <col width="21" customWidth="1" min="78" max="78"/>
-    <col width="22" customWidth="1" min="79" max="79"/>
-    <col width="14" customWidth="1" min="80" max="80"/>
+    <col width="21" customWidth="1" min="79" max="79"/>
+    <col width="33" customWidth="1" min="80" max="80"/>
+    <col width="22" customWidth="1" min="81" max="81"/>
+    <col width="14" customWidth="1" min="82" max="82"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -1543,30 +1545,40 @@
       </c>
       <c r="BW1" s="1" t="inlineStr">
         <is>
+          <t>limited_support_hours</t>
+        </is>
+      </c>
+      <c r="BX1" s="1" t="inlineStr">
+        <is>
           <t>ood_hours</t>
         </is>
       </c>
-      <c r="BX1" s="1" t="inlineStr">
+      <c r="BY1" s="1" t="inlineStr">
         <is>
           <t>not_evaluable_hours</t>
         </is>
       </c>
-      <c r="BY1" s="1" t="inlineStr">
+      <c r="BZ1" s="1" t="inlineStr">
         <is>
           <t>post_ref_share</t>
         </is>
       </c>
-      <c r="BZ1" s="1" t="inlineStr">
+      <c r="CA1" s="1" t="inlineStr">
         <is>
           <t>coverage_loss_hours</t>
         </is>
       </c>
-      <c r="CA1" s="1" t="inlineStr">
+      <c r="CB1" s="1" t="inlineStr">
+        <is>
+          <t>support_attributable_loss_hours</t>
+        </is>
+      </c>
+      <c r="CC1" s="1" t="inlineStr">
         <is>
           <t>report_coverage_rate</t>
         </is>
       </c>
-      <c r="CB1" s="1" t="inlineStr">
+      <c r="CD1" s="1" t="inlineStr">
         <is>
           <t>regime_label</t>
         </is>
@@ -1850,7 +1862,13 @@
       <c r="CA2" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="CB2" s="2" t="inlineStr">
+      <c r="CB2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD2" s="2" t="inlineStr">
         <is>
           <t>R0</t>
         </is>
@@ -2134,7 +2152,13 @@
       <c r="CA3" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="CB3" s="2" t="inlineStr">
+      <c r="CB3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD3" s="2" t="inlineStr">
         <is>
           <t>R1</t>
         </is>
@@ -2404,21 +2428,27 @@
         <v>0</v>
       </c>
       <c r="BW4" s="2" t="n">
+        <v>1542</v>
+      </c>
+      <c r="BX4" s="2" t="n">
         <v>131</v>
       </c>
-      <c r="BX4" s="2" t="n">
+      <c r="BY4" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="BY4" s="2" t="n">
+      <c r="BZ4" s="2" t="n">
         <v>0.07142857142857142</v>
       </c>
-      <c r="BZ4" s="2" t="n">
+      <c r="CA4" s="2" t="n">
         <v>1675</v>
       </c>
-      <c r="CA4" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="CB4" s="2" t="inlineStr">
+      <c r="CB4" s="2" t="n">
+        <v>1542</v>
+      </c>
+      <c r="CC4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD4" s="2" t="inlineStr">
         <is>
           <t>R2</t>
         </is>
@@ -2702,7 +2732,13 @@
       <c r="CA5" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="CB5" s="2" t="inlineStr">
+      <c r="CB5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD5" s="2" t="inlineStr">
         <is>
           <t>R3</t>
         </is>
@@ -2986,7 +3022,13 @@
       <c r="CA6" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="CB6" s="2" t="inlineStr">
+      <c r="CB6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD6" s="2" t="inlineStr">
         <is>
           <t>R0</t>
         </is>
@@ -3270,7 +3312,13 @@
       <c r="CA7" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="CB7" s="2" t="inlineStr">
+      <c r="CB7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD7" s="2" t="inlineStr">
         <is>
           <t>R1</t>
         </is>
@@ -3540,21 +3588,27 @@
         <v>0</v>
       </c>
       <c r="BW8" s="2" t="n">
+        <v>1542</v>
+      </c>
+      <c r="BX8" s="2" t="n">
         <v>131</v>
       </c>
-      <c r="BX8" s="2" t="n">
+      <c r="BY8" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="BY8" s="2" t="n">
+      <c r="BZ8" s="2" t="n">
         <v>0.07142857142857142</v>
       </c>
-      <c r="BZ8" s="2" t="n">
+      <c r="CA8" s="2" t="n">
         <v>1675</v>
       </c>
-      <c r="CA8" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="CB8" s="2" t="inlineStr">
+      <c r="CB8" s="2" t="n">
+        <v>1542</v>
+      </c>
+      <c r="CC8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD8" s="2" t="inlineStr">
         <is>
           <t>R2</t>
         </is>
@@ -3838,7 +3892,13 @@
       <c r="CA9" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="CB9" s="2" t="inlineStr">
+      <c r="CB9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD9" s="2" t="inlineStr">
         <is>
           <t>R3</t>
         </is>
@@ -4122,7 +4182,13 @@
       <c r="CA10" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="CB10" s="2" t="inlineStr">
+      <c r="CB10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD10" s="2" t="inlineStr">
         <is>
           <t>R0</t>
         </is>
@@ -4406,7 +4472,13 @@
       <c r="CA11" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="CB11" s="2" t="inlineStr">
+      <c r="CB11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD11" s="2" t="inlineStr">
         <is>
           <t>R1</t>
         </is>
@@ -4676,21 +4748,27 @@
         <v>0</v>
       </c>
       <c r="BW12" s="2" t="n">
+        <v>1542</v>
+      </c>
+      <c r="BX12" s="2" t="n">
         <v>131</v>
       </c>
-      <c r="BX12" s="2" t="n">
+      <c r="BY12" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="BY12" s="2" t="n">
+      <c r="BZ12" s="2" t="n">
         <v>0.07142857142857142</v>
       </c>
-      <c r="BZ12" s="2" t="n">
+      <c r="CA12" s="2" t="n">
         <v>1675</v>
       </c>
-      <c r="CA12" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="CB12" s="2" t="inlineStr">
+      <c r="CB12" s="2" t="n">
+        <v>1542</v>
+      </c>
+      <c r="CC12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD12" s="2" t="inlineStr">
         <is>
           <t>R2</t>
         </is>
@@ -4974,7 +5052,13 @@
       <c r="CA13" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="CB13" s="2" t="inlineStr">
+      <c r="CB13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD13" s="2" t="inlineStr">
         <is>
           <t>R3</t>
         </is>
@@ -5258,7 +5342,13 @@
       <c r="CA14" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="CB14" s="2" t="inlineStr">
+      <c r="CB14" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC14" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD14" s="2" t="inlineStr">
         <is>
           <t>R0</t>
         </is>
@@ -5542,7 +5632,13 @@
       <c r="CA15" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="CB15" s="2" t="inlineStr">
+      <c r="CB15" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC15" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD15" s="2" t="inlineStr">
         <is>
           <t>R1</t>
         </is>
@@ -5812,21 +5908,27 @@
         <v>0</v>
       </c>
       <c r="BW16" s="2" t="n">
+        <v>1542</v>
+      </c>
+      <c r="BX16" s="2" t="n">
         <v>131</v>
       </c>
-      <c r="BX16" s="2" t="n">
+      <c r="BY16" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="BY16" s="2" t="n">
+      <c r="BZ16" s="2" t="n">
         <v>0.07142857142857142</v>
       </c>
-      <c r="BZ16" s="2" t="n">
+      <c r="CA16" s="2" t="n">
         <v>1675</v>
       </c>
-      <c r="CA16" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="CB16" s="2" t="inlineStr">
+      <c r="CB16" s="2" t="n">
+        <v>1542</v>
+      </c>
+      <c r="CC16" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD16" s="2" t="inlineStr">
         <is>
           <t>R2</t>
         </is>
@@ -6110,7 +6212,13 @@
       <c r="CA17" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="CB17" s="2" t="inlineStr">
+      <c r="CB17" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC17" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD17" s="2" t="inlineStr">
         <is>
           <t>R3</t>
         </is>
@@ -6394,7 +6502,13 @@
       <c r="CA18" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="CB18" s="2" t="inlineStr">
+      <c r="CB18" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC18" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD18" s="2" t="inlineStr">
         <is>
           <t>R0</t>
         </is>
@@ -6678,7 +6792,13 @@
       <c r="CA19" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="CB19" s="2" t="inlineStr">
+      <c r="CB19" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC19" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD19" s="2" t="inlineStr">
         <is>
           <t>R1</t>
         </is>
@@ -6948,21 +7068,27 @@
         <v>0</v>
       </c>
       <c r="BW20" s="2" t="n">
+        <v>1542</v>
+      </c>
+      <c r="BX20" s="2" t="n">
         <v>131</v>
       </c>
-      <c r="BX20" s="2" t="n">
+      <c r="BY20" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="BY20" s="2" t="n">
+      <c r="BZ20" s="2" t="n">
         <v>0.07142857142857142</v>
       </c>
-      <c r="BZ20" s="2" t="n">
+      <c r="CA20" s="2" t="n">
         <v>1675</v>
       </c>
-      <c r="CA20" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="CB20" s="2" t="inlineStr">
+      <c r="CB20" s="2" t="n">
+        <v>1542</v>
+      </c>
+      <c r="CC20" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD20" s="2" t="inlineStr">
         <is>
           <t>R2</t>
         </is>
@@ -7246,7 +7372,13 @@
       <c r="CA21" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="CB21" s="2" t="inlineStr">
+      <c r="CB21" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC21" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD21" s="2" t="inlineStr">
         <is>
           <t>R3</t>
         </is>
@@ -7530,7 +7662,13 @@
       <c r="CA22" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="CB22" s="2" t="inlineStr">
+      <c r="CB22" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC22" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD22" s="2" t="inlineStr">
         <is>
           <t>R0</t>
         </is>
@@ -7814,7 +7952,13 @@
       <c r="CA23" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="CB23" s="2" t="inlineStr">
+      <c r="CB23" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC23" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD23" s="2" t="inlineStr">
         <is>
           <t>R1</t>
         </is>
@@ -8084,21 +8228,27 @@
         <v>0</v>
       </c>
       <c r="BW24" s="2" t="n">
+        <v>1542</v>
+      </c>
+      <c r="BX24" s="2" t="n">
         <v>131</v>
       </c>
-      <c r="BX24" s="2" t="n">
+      <c r="BY24" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="BY24" s="2" t="n">
+      <c r="BZ24" s="2" t="n">
         <v>0.07142857142857142</v>
       </c>
-      <c r="BZ24" s="2" t="n">
+      <c r="CA24" s="2" t="n">
         <v>1675</v>
       </c>
-      <c r="CA24" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="CB24" s="2" t="inlineStr">
+      <c r="CB24" s="2" t="n">
+        <v>1542</v>
+      </c>
+      <c r="CC24" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD24" s="2" t="inlineStr">
         <is>
           <t>R2</t>
         </is>
@@ -8382,7 +8532,13 @@
       <c r="CA25" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="CB25" s="2" t="inlineStr">
+      <c r="CB25" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC25" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD25" s="2" t="inlineStr">
         <is>
           <t>R3</t>
         </is>
@@ -8666,7 +8822,13 @@
       <c r="CA26" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="CB26" s="2" t="inlineStr">
+      <c r="CB26" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC26" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD26" s="2" t="inlineStr">
         <is>
           <t>R0</t>
         </is>
@@ -8950,7 +9112,13 @@
       <c r="CA27" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="CB27" s="2" t="inlineStr">
+      <c r="CB27" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC27" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD27" s="2" t="inlineStr">
         <is>
           <t>R1</t>
         </is>
@@ -9220,21 +9388,27 @@
         <v>0</v>
       </c>
       <c r="BW28" s="2" t="n">
+        <v>1542</v>
+      </c>
+      <c r="BX28" s="2" t="n">
         <v>131</v>
       </c>
-      <c r="BX28" s="2" t="n">
+      <c r="BY28" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="BY28" s="2" t="n">
+      <c r="BZ28" s="2" t="n">
         <v>0.07142857142857142</v>
       </c>
-      <c r="BZ28" s="2" t="n">
+      <c r="CA28" s="2" t="n">
         <v>1675</v>
       </c>
-      <c r="CA28" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="CB28" s="2" t="inlineStr">
+      <c r="CB28" s="2" t="n">
+        <v>1542</v>
+      </c>
+      <c r="CC28" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD28" s="2" t="inlineStr">
         <is>
           <t>R2</t>
         </is>
@@ -9518,7 +9692,13 @@
       <c r="CA29" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="CB29" s="2" t="inlineStr">
+      <c r="CB29" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC29" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD29" s="2" t="inlineStr">
         <is>
           <t>R3</t>
         </is>
@@ -9802,7 +9982,13 @@
       <c r="CA30" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="CB30" s="2" t="inlineStr">
+      <c r="CB30" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC30" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD30" s="2" t="inlineStr">
         <is>
           <t>R0</t>
         </is>
@@ -10086,7 +10272,13 @@
       <c r="CA31" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="CB31" s="2" t="inlineStr">
+      <c r="CB31" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC31" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD31" s="2" t="inlineStr">
         <is>
           <t>R1</t>
         </is>
@@ -10356,21 +10548,27 @@
         <v>0</v>
       </c>
       <c r="BW32" s="2" t="n">
+        <v>1542</v>
+      </c>
+      <c r="BX32" s="2" t="n">
         <v>131</v>
       </c>
-      <c r="BX32" s="2" t="n">
+      <c r="BY32" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="BY32" s="2" t="n">
+      <c r="BZ32" s="2" t="n">
         <v>0.07142857142857142</v>
       </c>
-      <c r="BZ32" s="2" t="n">
+      <c r="CA32" s="2" t="n">
         <v>1675</v>
       </c>
-      <c r="CA32" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="CB32" s="2" t="inlineStr">
+      <c r="CB32" s="2" t="n">
+        <v>1542</v>
+      </c>
+      <c r="CC32" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD32" s="2" t="inlineStr">
         <is>
           <t>R2</t>
         </is>
@@ -10654,7 +10852,13 @@
       <c r="CA33" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="CB33" s="2" t="inlineStr">
+      <c r="CB33" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC33" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD33" s="2" t="inlineStr">
         <is>
           <t>R3</t>
         </is>
@@ -10938,7 +11142,13 @@
       <c r="CA34" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="CB34" s="2" t="inlineStr">
+      <c r="CB34" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC34" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD34" s="2" t="inlineStr">
         <is>
           <t>R0</t>
         </is>
@@ -11222,7 +11432,13 @@
       <c r="CA35" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="CB35" s="2" t="inlineStr">
+      <c r="CB35" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC35" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD35" s="2" t="inlineStr">
         <is>
           <t>R1</t>
         </is>
@@ -11492,21 +11708,27 @@
         <v>0</v>
       </c>
       <c r="BW36" s="2" t="n">
+        <v>1542</v>
+      </c>
+      <c r="BX36" s="2" t="n">
         <v>131</v>
       </c>
-      <c r="BX36" s="2" t="n">
+      <c r="BY36" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="BY36" s="2" t="n">
+      <c r="BZ36" s="2" t="n">
         <v>0.07142857142857142</v>
       </c>
-      <c r="BZ36" s="2" t="n">
+      <c r="CA36" s="2" t="n">
         <v>1675</v>
       </c>
-      <c r="CA36" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="CB36" s="2" t="inlineStr">
+      <c r="CB36" s="2" t="n">
+        <v>1542</v>
+      </c>
+      <c r="CC36" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD36" s="2" t="inlineStr">
         <is>
           <t>R2</t>
         </is>
@@ -11790,7 +12012,13 @@
       <c r="CA37" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="CB37" s="2" t="inlineStr">
+      <c r="CB37" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC37" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD37" s="2" t="inlineStr">
         <is>
           <t>R3</t>
         </is>
@@ -12074,7 +12302,13 @@
       <c r="CA38" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="CB38" s="2" t="inlineStr">
+      <c r="CB38" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC38" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD38" s="2" t="inlineStr">
         <is>
           <t>R0</t>
         </is>
@@ -12358,7 +12592,13 @@
       <c r="CA39" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="CB39" s="2" t="inlineStr">
+      <c r="CB39" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC39" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD39" s="2" t="inlineStr">
         <is>
           <t>R1</t>
         </is>
@@ -12628,21 +12868,27 @@
         <v>0</v>
       </c>
       <c r="BW40" s="2" t="n">
+        <v>1542</v>
+      </c>
+      <c r="BX40" s="2" t="n">
         <v>131</v>
       </c>
-      <c r="BX40" s="2" t="n">
+      <c r="BY40" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="BY40" s="2" t="n">
+      <c r="BZ40" s="2" t="n">
         <v>0.07142857142857142</v>
       </c>
-      <c r="BZ40" s="2" t="n">
+      <c r="CA40" s="2" t="n">
         <v>1675</v>
       </c>
-      <c r="CA40" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="CB40" s="2" t="inlineStr">
+      <c r="CB40" s="2" t="n">
+        <v>1542</v>
+      </c>
+      <c r="CC40" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD40" s="2" t="inlineStr">
         <is>
           <t>R2</t>
         </is>
@@ -12926,7 +13172,13 @@
       <c r="CA41" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="CB41" s="2" t="inlineStr">
+      <c r="CB41" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC41" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD41" s="2" t="inlineStr">
         <is>
           <t>R3</t>
         </is>
@@ -13210,7 +13462,13 @@
       <c r="CA42" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="CB42" s="2" t="inlineStr">
+      <c r="CB42" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC42" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD42" s="2" t="inlineStr">
         <is>
           <t>R0</t>
         </is>
@@ -13494,7 +13752,13 @@
       <c r="CA43" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="CB43" s="2" t="inlineStr">
+      <c r="CB43" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC43" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD43" s="2" t="inlineStr">
         <is>
           <t>R1</t>
         </is>
@@ -13764,21 +14028,27 @@
         <v>0</v>
       </c>
       <c r="BW44" s="2" t="n">
+        <v>1542</v>
+      </c>
+      <c r="BX44" s="2" t="n">
         <v>131</v>
       </c>
-      <c r="BX44" s="2" t="n">
+      <c r="BY44" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="BY44" s="2" t="n">
+      <c r="BZ44" s="2" t="n">
         <v>0.07142857142857142</v>
       </c>
-      <c r="BZ44" s="2" t="n">
+      <c r="CA44" s="2" t="n">
         <v>1675</v>
       </c>
-      <c r="CA44" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="CB44" s="2" t="inlineStr">
+      <c r="CB44" s="2" t="n">
+        <v>1542</v>
+      </c>
+      <c r="CC44" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD44" s="2" t="inlineStr">
         <is>
           <t>R2</t>
         </is>
@@ -14062,7 +14332,13 @@
       <c r="CA45" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="CB45" s="2" t="inlineStr">
+      <c r="CB45" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC45" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD45" s="2" t="inlineStr">
         <is>
           <t>R3</t>
         </is>
@@ -14346,7 +14622,13 @@
       <c r="CA46" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="CB46" s="2" t="inlineStr">
+      <c r="CB46" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC46" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD46" s="2" t="inlineStr">
         <is>
           <t>R0</t>
         </is>
@@ -14630,7 +14912,13 @@
       <c r="CA47" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="CB47" s="2" t="inlineStr">
+      <c r="CB47" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC47" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD47" s="2" t="inlineStr">
         <is>
           <t>R1</t>
         </is>
@@ -14900,21 +15188,27 @@
         <v>0</v>
       </c>
       <c r="BW48" s="2" t="n">
+        <v>1542</v>
+      </c>
+      <c r="BX48" s="2" t="n">
         <v>131</v>
       </c>
-      <c r="BX48" s="2" t="n">
+      <c r="BY48" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="BY48" s="2" t="n">
+      <c r="BZ48" s="2" t="n">
         <v>0.07142857142857142</v>
       </c>
-      <c r="BZ48" s="2" t="n">
+      <c r="CA48" s="2" t="n">
         <v>1675</v>
       </c>
-      <c r="CA48" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="CB48" s="2" t="inlineStr">
+      <c r="CB48" s="2" t="n">
+        <v>1542</v>
+      </c>
+      <c r="CC48" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD48" s="2" t="inlineStr">
         <is>
           <t>R2</t>
         </is>
@@ -15198,7 +15492,13 @@
       <c r="CA49" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="CB49" s="2" t="inlineStr">
+      <c r="CB49" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC49" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD49" s="2" t="inlineStr">
         <is>
           <t>R3</t>
         </is>
@@ -15482,7 +15782,13 @@
       <c r="CA50" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="CB50" s="2" t="inlineStr">
+      <c r="CB50" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC50" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD50" s="2" t="inlineStr">
         <is>
           <t>R0</t>
         </is>
@@ -15766,7 +16072,13 @@
       <c r="CA51" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="CB51" s="2" t="inlineStr">
+      <c r="CB51" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC51" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD51" s="2" t="inlineStr">
         <is>
           <t>R1</t>
         </is>
@@ -16036,21 +16348,27 @@
         <v>0</v>
       </c>
       <c r="BW52" s="2" t="n">
+        <v>1542</v>
+      </c>
+      <c r="BX52" s="2" t="n">
         <v>131</v>
       </c>
-      <c r="BX52" s="2" t="n">
+      <c r="BY52" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="BY52" s="2" t="n">
+      <c r="BZ52" s="2" t="n">
         <v>0.07142857142857142</v>
       </c>
-      <c r="BZ52" s="2" t="n">
+      <c r="CA52" s="2" t="n">
         <v>1675</v>
       </c>
-      <c r="CA52" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="CB52" s="2" t="inlineStr">
+      <c r="CB52" s="2" t="n">
+        <v>1542</v>
+      </c>
+      <c r="CC52" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD52" s="2" t="inlineStr">
         <is>
           <t>R2</t>
         </is>
@@ -16334,7 +16652,13 @@
       <c r="CA53" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="CB53" s="2" t="inlineStr">
+      <c r="CB53" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC53" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD53" s="2" t="inlineStr">
         <is>
           <t>R3</t>
         </is>
@@ -16618,7 +16942,13 @@
       <c r="CA54" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="CB54" s="2" t="inlineStr">
+      <c r="CB54" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC54" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD54" s="2" t="inlineStr">
         <is>
           <t>R0</t>
         </is>
@@ -16902,7 +17232,13 @@
       <c r="CA55" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="CB55" s="2" t="inlineStr">
+      <c r="CB55" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC55" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD55" s="2" t="inlineStr">
         <is>
           <t>R1</t>
         </is>
@@ -17172,21 +17508,27 @@
         <v>0</v>
       </c>
       <c r="BW56" s="2" t="n">
+        <v>1542</v>
+      </c>
+      <c r="BX56" s="2" t="n">
         <v>131</v>
       </c>
-      <c r="BX56" s="2" t="n">
+      <c r="BY56" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="BY56" s="2" t="n">
+      <c r="BZ56" s="2" t="n">
         <v>0.07142857142857142</v>
       </c>
-      <c r="BZ56" s="2" t="n">
+      <c r="CA56" s="2" t="n">
         <v>1675</v>
       </c>
-      <c r="CA56" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="CB56" s="2" t="inlineStr">
+      <c r="CB56" s="2" t="n">
+        <v>1542</v>
+      </c>
+      <c r="CC56" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD56" s="2" t="inlineStr">
         <is>
           <t>R2</t>
         </is>
@@ -17470,14 +17812,20 @@
       <c r="CA57" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="CB57" s="2" t="inlineStr">
+      <c r="CB57" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC57" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD57" s="2" t="inlineStr">
         <is>
           <t>R3</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:CB57"/>
+  <autoFilter ref="A1:CD57"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -17488,7 +17836,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CI15"/>
+  <dimension ref="A1:CK15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -17565,19 +17913,21 @@
     <col width="22" customWidth="1" min="72" max="72"/>
     <col width="23" customWidth="1" min="73" max="73"/>
     <col width="23" customWidth="1" min="74" max="74"/>
-    <col width="11" customWidth="1" min="75" max="75"/>
-    <col width="21" customWidth="1" min="76" max="76"/>
+    <col width="23" customWidth="1" min="75" max="75"/>
+    <col width="11" customWidth="1" min="76" max="76"/>
     <col width="21" customWidth="1" min="77" max="77"/>
     <col width="21" customWidth="1" min="78" max="78"/>
-    <col width="22" customWidth="1" min="79" max="79"/>
-    <col width="14" customWidth="1" min="80" max="80"/>
-    <col width="13" customWidth="1" min="81" max="81"/>
-    <col width="15" customWidth="1" min="82" max="82"/>
-    <col width="11" customWidth="1" min="83" max="83"/>
-    <col width="13" customWidth="1" min="84" max="84"/>
-    <col width="15" customWidth="1" min="85" max="85"/>
+    <col width="21" customWidth="1" min="79" max="79"/>
+    <col width="33" customWidth="1" min="80" max="80"/>
+    <col width="22" customWidth="1" min="81" max="81"/>
+    <col width="14" customWidth="1" min="82" max="82"/>
+    <col width="13" customWidth="1" min="83" max="83"/>
+    <col width="15" customWidth="1" min="84" max="84"/>
+    <col width="11" customWidth="1" min="85" max="85"/>
     <col width="13" customWidth="1" min="86" max="86"/>
-    <col width="17" customWidth="1" min="87" max="87"/>
+    <col width="15" customWidth="1" min="87" max="87"/>
+    <col width="13" customWidth="1" min="88" max="88"/>
+    <col width="17" customWidth="1" min="89" max="89"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -17953,65 +18303,75 @@
       </c>
       <c r="BW1" s="1" t="inlineStr">
         <is>
+          <t>limited_support_hours</t>
+        </is>
+      </c>
+      <c r="BX1" s="1" t="inlineStr">
+        <is>
           <t>ood_hours</t>
         </is>
       </c>
-      <c r="BX1" s="1" t="inlineStr">
+      <c r="BY1" s="1" t="inlineStr">
         <is>
           <t>not_evaluable_hours</t>
         </is>
       </c>
-      <c r="BY1" s="1" t="inlineStr">
+      <c r="BZ1" s="1" t="inlineStr">
         <is>
           <t>post_ref_share</t>
         </is>
       </c>
-      <c r="BZ1" s="1" t="inlineStr">
+      <c r="CA1" s="1" t="inlineStr">
         <is>
           <t>coverage_loss_hours</t>
         </is>
       </c>
-      <c r="CA1" s="1" t="inlineStr">
+      <c r="CB1" s="1" t="inlineStr">
+        <is>
+          <t>support_attributable_loss_hours</t>
+        </is>
+      </c>
+      <c r="CC1" s="1" t="inlineStr">
         <is>
           <t>report_coverage_rate</t>
         </is>
       </c>
-      <c r="CB1" s="1" t="inlineStr">
+      <c r="CD1" s="1" t="inlineStr">
         <is>
           <t>regime_label</t>
         </is>
       </c>
-      <c r="CC1" s="1" t="inlineStr">
+      <c r="CE1" s="1" t="inlineStr">
         <is>
           <t>family_days</t>
         </is>
       </c>
-      <c r="CD1" s="1" t="inlineStr">
+      <c r="CF1" s="1" t="inlineStr">
         <is>
           <t>family_months</t>
         </is>
       </c>
-      <c r="CE1" s="1" t="inlineStr">
+      <c r="CG1" s="1" t="inlineStr">
         <is>
           <t>node_days</t>
         </is>
       </c>
-      <c r="CF1" s="1" t="inlineStr">
+      <c r="CH1" s="1" t="inlineStr">
         <is>
           <t>node_months</t>
         </is>
       </c>
-      <c r="CG1" s="1" t="inlineStr">
+      <c r="CI1" s="1" t="inlineStr">
         <is>
           <t>node_coverage</t>
         </is>
       </c>
-      <c r="CH1" s="1" t="inlineStr">
+      <c r="CJ1" s="1" t="inlineStr">
         <is>
           <t>blocker_set</t>
         </is>
       </c>
-      <c r="CI1" s="1" t="inlineStr">
+      <c r="CK1" s="1" t="inlineStr">
         <is>
           <t>primary_blocker</t>
         </is>
@@ -18281,33 +18641,33 @@
         <v>0</v>
       </c>
       <c r="BW2" s="2" t="n">
+        <v>1542</v>
+      </c>
+      <c r="BX2" s="2" t="n">
         <v>131</v>
       </c>
-      <c r="BX2" s="2" t="n">
+      <c r="BY2" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="BY2" s="2" t="n">
+      <c r="BZ2" s="2" t="n">
         <v>0.07142857142857142</v>
       </c>
-      <c r="BZ2" s="2" t="n">
+      <c r="CA2" s="2" t="n">
         <v>1675</v>
       </c>
-      <c r="CA2" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="CB2" s="2" t="inlineStr">
+      <c r="CB2" s="2" t="n">
+        <v>1542</v>
+      </c>
+      <c r="CC2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD2" s="2" t="inlineStr">
         <is>
           <t>R2</t>
         </is>
       </c>
-      <c r="CC2" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="CD2" s="2" t="b">
-        <v>0</v>
-      </c>
       <c r="CE2" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CF2" s="2" t="b">
         <v>0</v>
@@ -18315,12 +18675,18 @@
       <c r="CG2" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="CH2" s="2" t="inlineStr">
+      <c r="CH2" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="CI2" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="CJ2" s="2" t="inlineStr">
         <is>
           <t>family_days</t>
         </is>
       </c>
-      <c r="CI2" s="2" t="inlineStr">
+      <c r="CK2" s="2" t="inlineStr">
         <is>
           <t>family_days</t>
         </is>
@@ -18590,33 +18956,33 @@
         <v>0</v>
       </c>
       <c r="BW3" s="2" t="n">
+        <v>1542</v>
+      </c>
+      <c r="BX3" s="2" t="n">
         <v>131</v>
       </c>
-      <c r="BX3" s="2" t="n">
+      <c r="BY3" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="BY3" s="2" t="n">
+      <c r="BZ3" s="2" t="n">
         <v>0.07142857142857142</v>
       </c>
-      <c r="BZ3" s="2" t="n">
+      <c r="CA3" s="2" t="n">
         <v>1675</v>
       </c>
-      <c r="CA3" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="CB3" s="2" t="inlineStr">
+      <c r="CB3" s="2" t="n">
+        <v>1542</v>
+      </c>
+      <c r="CC3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD3" s="2" t="inlineStr">
         <is>
           <t>R2</t>
         </is>
       </c>
-      <c r="CC3" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="CD3" s="2" t="b">
-        <v>0</v>
-      </c>
       <c r="CE3" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CF3" s="2" t="b">
         <v>0</v>
@@ -18624,12 +18990,18 @@
       <c r="CG3" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="CH3" s="2" t="inlineStr">
+      <c r="CH3" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="CI3" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="CJ3" s="2" t="inlineStr">
         <is>
           <t>family_days</t>
         </is>
       </c>
-      <c r="CI3" s="2" t="inlineStr">
+      <c r="CK3" s="2" t="inlineStr">
         <is>
           <t>family_days</t>
         </is>
@@ -18899,33 +19271,33 @@
         <v>0</v>
       </c>
       <c r="BW4" s="2" t="n">
+        <v>1542</v>
+      </c>
+      <c r="BX4" s="2" t="n">
         <v>131</v>
       </c>
-      <c r="BX4" s="2" t="n">
+      <c r="BY4" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="BY4" s="2" t="n">
+      <c r="BZ4" s="2" t="n">
         <v>0.07142857142857142</v>
       </c>
-      <c r="BZ4" s="2" t="n">
+      <c r="CA4" s="2" t="n">
         <v>1675</v>
       </c>
-      <c r="CA4" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="CB4" s="2" t="inlineStr">
+      <c r="CB4" s="2" t="n">
+        <v>1542</v>
+      </c>
+      <c r="CC4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD4" s="2" t="inlineStr">
         <is>
           <t>R2</t>
         </is>
       </c>
-      <c r="CC4" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="CD4" s="2" t="b">
-        <v>0</v>
-      </c>
       <c r="CE4" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CF4" s="2" t="b">
         <v>0</v>
@@ -18933,12 +19305,18 @@
       <c r="CG4" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="CH4" s="2" t="inlineStr">
+      <c r="CH4" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="CI4" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="CJ4" s="2" t="inlineStr">
         <is>
           <t>family_days</t>
         </is>
       </c>
-      <c r="CI4" s="2" t="inlineStr">
+      <c r="CK4" s="2" t="inlineStr">
         <is>
           <t>family_days</t>
         </is>
@@ -19208,33 +19586,33 @@
         <v>0</v>
       </c>
       <c r="BW5" s="2" t="n">
+        <v>1542</v>
+      </c>
+      <c r="BX5" s="2" t="n">
         <v>131</v>
       </c>
-      <c r="BX5" s="2" t="n">
+      <c r="BY5" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="BY5" s="2" t="n">
+      <c r="BZ5" s="2" t="n">
         <v>0.07142857142857142</v>
       </c>
-      <c r="BZ5" s="2" t="n">
+      <c r="CA5" s="2" t="n">
         <v>1675</v>
       </c>
-      <c r="CA5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="CB5" s="2" t="inlineStr">
+      <c r="CB5" s="2" t="n">
+        <v>1542</v>
+      </c>
+      <c r="CC5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD5" s="2" t="inlineStr">
         <is>
           <t>R2</t>
         </is>
       </c>
-      <c r="CC5" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="CD5" s="2" t="b">
-        <v>0</v>
-      </c>
       <c r="CE5" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CF5" s="2" t="b">
         <v>0</v>
@@ -19242,12 +19620,18 @@
       <c r="CG5" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="CH5" s="2" t="inlineStr">
+      <c r="CH5" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="CI5" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="CJ5" s="2" t="inlineStr">
         <is>
           <t>family_days</t>
         </is>
       </c>
-      <c r="CI5" s="2" t="inlineStr">
+      <c r="CK5" s="2" t="inlineStr">
         <is>
           <t>family_days</t>
         </is>
@@ -19517,33 +19901,33 @@
         <v>0</v>
       </c>
       <c r="BW6" s="2" t="n">
+        <v>1542</v>
+      </c>
+      <c r="BX6" s="2" t="n">
         <v>131</v>
       </c>
-      <c r="BX6" s="2" t="n">
+      <c r="BY6" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="BY6" s="2" t="n">
+      <c r="BZ6" s="2" t="n">
         <v>0.07142857142857142</v>
       </c>
-      <c r="BZ6" s="2" t="n">
+      <c r="CA6" s="2" t="n">
         <v>1675</v>
       </c>
-      <c r="CA6" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="CB6" s="2" t="inlineStr">
+      <c r="CB6" s="2" t="n">
+        <v>1542</v>
+      </c>
+      <c r="CC6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD6" s="2" t="inlineStr">
         <is>
           <t>R2</t>
         </is>
       </c>
-      <c r="CC6" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="CD6" s="2" t="b">
-        <v>0</v>
-      </c>
       <c r="CE6" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CF6" s="2" t="b">
         <v>0</v>
@@ -19551,12 +19935,18 @@
       <c r="CG6" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="CH6" s="2" t="inlineStr">
+      <c r="CH6" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="CI6" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="CJ6" s="2" t="inlineStr">
         <is>
           <t>family_days</t>
         </is>
       </c>
-      <c r="CI6" s="2" t="inlineStr">
+      <c r="CK6" s="2" t="inlineStr">
         <is>
           <t>family_days</t>
         </is>
@@ -19826,33 +20216,33 @@
         <v>0</v>
       </c>
       <c r="BW7" s="2" t="n">
+        <v>1542</v>
+      </c>
+      <c r="BX7" s="2" t="n">
         <v>131</v>
       </c>
-      <c r="BX7" s="2" t="n">
+      <c r="BY7" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="BY7" s="2" t="n">
+      <c r="BZ7" s="2" t="n">
         <v>0.07142857142857142</v>
       </c>
-      <c r="BZ7" s="2" t="n">
+      <c r="CA7" s="2" t="n">
         <v>1675</v>
       </c>
-      <c r="CA7" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="CB7" s="2" t="inlineStr">
+      <c r="CB7" s="2" t="n">
+        <v>1542</v>
+      </c>
+      <c r="CC7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD7" s="2" t="inlineStr">
         <is>
           <t>R2</t>
         </is>
       </c>
-      <c r="CC7" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="CD7" s="2" t="b">
-        <v>0</v>
-      </c>
       <c r="CE7" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CF7" s="2" t="b">
         <v>0</v>
@@ -19860,12 +20250,18 @@
       <c r="CG7" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="CH7" s="2" t="inlineStr">
+      <c r="CH7" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="CI7" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="CJ7" s="2" t="inlineStr">
         <is>
           <t>family_days</t>
         </is>
       </c>
-      <c r="CI7" s="2" t="inlineStr">
+      <c r="CK7" s="2" t="inlineStr">
         <is>
           <t>family_days</t>
         </is>
@@ -20135,33 +20531,33 @@
         <v>0</v>
       </c>
       <c r="BW8" s="2" t="n">
+        <v>1542</v>
+      </c>
+      <c r="BX8" s="2" t="n">
         <v>131</v>
       </c>
-      <c r="BX8" s="2" t="n">
+      <c r="BY8" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="BY8" s="2" t="n">
+      <c r="BZ8" s="2" t="n">
         <v>0.07142857142857142</v>
       </c>
-      <c r="BZ8" s="2" t="n">
+      <c r="CA8" s="2" t="n">
         <v>1675</v>
       </c>
-      <c r="CA8" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="CB8" s="2" t="inlineStr">
+      <c r="CB8" s="2" t="n">
+        <v>1542</v>
+      </c>
+      <c r="CC8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD8" s="2" t="inlineStr">
         <is>
           <t>R2</t>
         </is>
       </c>
-      <c r="CC8" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="CD8" s="2" t="b">
-        <v>0</v>
-      </c>
       <c r="CE8" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CF8" s="2" t="b">
         <v>0</v>
@@ -20169,12 +20565,18 @@
       <c r="CG8" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="CH8" s="2" t="inlineStr">
+      <c r="CH8" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="CI8" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="CJ8" s="2" t="inlineStr">
         <is>
           <t>family_days</t>
         </is>
       </c>
-      <c r="CI8" s="2" t="inlineStr">
+      <c r="CK8" s="2" t="inlineStr">
         <is>
           <t>family_days</t>
         </is>
@@ -20444,33 +20846,33 @@
         <v>0</v>
       </c>
       <c r="BW9" s="2" t="n">
+        <v>1542</v>
+      </c>
+      <c r="BX9" s="2" t="n">
         <v>131</v>
       </c>
-      <c r="BX9" s="2" t="n">
+      <c r="BY9" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="BY9" s="2" t="n">
+      <c r="BZ9" s="2" t="n">
         <v>0.07142857142857142</v>
       </c>
-      <c r="BZ9" s="2" t="n">
+      <c r="CA9" s="2" t="n">
         <v>1675</v>
       </c>
-      <c r="CA9" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="CB9" s="2" t="inlineStr">
+      <c r="CB9" s="2" t="n">
+        <v>1542</v>
+      </c>
+      <c r="CC9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD9" s="2" t="inlineStr">
         <is>
           <t>R2</t>
         </is>
       </c>
-      <c r="CC9" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="CD9" s="2" t="b">
-        <v>0</v>
-      </c>
       <c r="CE9" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CF9" s="2" t="b">
         <v>0</v>
@@ -20478,12 +20880,18 @@
       <c r="CG9" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="CH9" s="2" t="inlineStr">
+      <c r="CH9" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="CI9" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="CJ9" s="2" t="inlineStr">
         <is>
           <t>family_days</t>
         </is>
       </c>
-      <c r="CI9" s="2" t="inlineStr">
+      <c r="CK9" s="2" t="inlineStr">
         <is>
           <t>family_days</t>
         </is>
@@ -20753,33 +21161,33 @@
         <v>0</v>
       </c>
       <c r="BW10" s="2" t="n">
+        <v>1542</v>
+      </c>
+      <c r="BX10" s="2" t="n">
         <v>131</v>
       </c>
-      <c r="BX10" s="2" t="n">
+      <c r="BY10" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="BY10" s="2" t="n">
+      <c r="BZ10" s="2" t="n">
         <v>0.07142857142857142</v>
       </c>
-      <c r="BZ10" s="2" t="n">
+      <c r="CA10" s="2" t="n">
         <v>1675</v>
       </c>
-      <c r="CA10" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="CB10" s="2" t="inlineStr">
+      <c r="CB10" s="2" t="n">
+        <v>1542</v>
+      </c>
+      <c r="CC10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD10" s="2" t="inlineStr">
         <is>
           <t>R2</t>
         </is>
       </c>
-      <c r="CC10" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="CD10" s="2" t="b">
-        <v>0</v>
-      </c>
       <c r="CE10" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CF10" s="2" t="b">
         <v>0</v>
@@ -20787,12 +21195,18 @@
       <c r="CG10" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="CH10" s="2" t="inlineStr">
+      <c r="CH10" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="CI10" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="CJ10" s="2" t="inlineStr">
         <is>
           <t>family_days</t>
         </is>
       </c>
-      <c r="CI10" s="2" t="inlineStr">
+      <c r="CK10" s="2" t="inlineStr">
         <is>
           <t>family_days</t>
         </is>
@@ -21062,33 +21476,33 @@
         <v>0</v>
       </c>
       <c r="BW11" s="2" t="n">
+        <v>1542</v>
+      </c>
+      <c r="BX11" s="2" t="n">
         <v>131</v>
       </c>
-      <c r="BX11" s="2" t="n">
+      <c r="BY11" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="BY11" s="2" t="n">
+      <c r="BZ11" s="2" t="n">
         <v>0.07142857142857142</v>
       </c>
-      <c r="BZ11" s="2" t="n">
+      <c r="CA11" s="2" t="n">
         <v>1675</v>
       </c>
-      <c r="CA11" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="CB11" s="2" t="inlineStr">
+      <c r="CB11" s="2" t="n">
+        <v>1542</v>
+      </c>
+      <c r="CC11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD11" s="2" t="inlineStr">
         <is>
           <t>R2</t>
         </is>
       </c>
-      <c r="CC11" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="CD11" s="2" t="b">
-        <v>0</v>
-      </c>
       <c r="CE11" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CF11" s="2" t="b">
         <v>0</v>
@@ -21096,12 +21510,18 @@
       <c r="CG11" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="CH11" s="2" t="inlineStr">
+      <c r="CH11" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="CI11" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="CJ11" s="2" t="inlineStr">
         <is>
           <t>family_days</t>
         </is>
       </c>
-      <c r="CI11" s="2" t="inlineStr">
+      <c r="CK11" s="2" t="inlineStr">
         <is>
           <t>family_days</t>
         </is>
@@ -21371,33 +21791,33 @@
         <v>0</v>
       </c>
       <c r="BW12" s="2" t="n">
+        <v>1542</v>
+      </c>
+      <c r="BX12" s="2" t="n">
         <v>131</v>
       </c>
-      <c r="BX12" s="2" t="n">
+      <c r="BY12" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="BY12" s="2" t="n">
+      <c r="BZ12" s="2" t="n">
         <v>0.07142857142857142</v>
       </c>
-      <c r="BZ12" s="2" t="n">
+      <c r="CA12" s="2" t="n">
         <v>1675</v>
       </c>
-      <c r="CA12" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="CB12" s="2" t="inlineStr">
+      <c r="CB12" s="2" t="n">
+        <v>1542</v>
+      </c>
+      <c r="CC12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD12" s="2" t="inlineStr">
         <is>
           <t>R2</t>
         </is>
       </c>
-      <c r="CC12" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="CD12" s="2" t="b">
-        <v>0</v>
-      </c>
       <c r="CE12" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CF12" s="2" t="b">
         <v>0</v>
@@ -21405,12 +21825,18 @@
       <c r="CG12" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="CH12" s="2" t="inlineStr">
+      <c r="CH12" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="CI12" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="CJ12" s="2" t="inlineStr">
         <is>
           <t>family_days</t>
         </is>
       </c>
-      <c r="CI12" s="2" t="inlineStr">
+      <c r="CK12" s="2" t="inlineStr">
         <is>
           <t>family_days</t>
         </is>
@@ -21680,33 +22106,33 @@
         <v>0</v>
       </c>
       <c r="BW13" s="2" t="n">
+        <v>1542</v>
+      </c>
+      <c r="BX13" s="2" t="n">
         <v>131</v>
       </c>
-      <c r="BX13" s="2" t="n">
+      <c r="BY13" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="BY13" s="2" t="n">
+      <c r="BZ13" s="2" t="n">
         <v>0.07142857142857142</v>
       </c>
-      <c r="BZ13" s="2" t="n">
+      <c r="CA13" s="2" t="n">
         <v>1675</v>
       </c>
-      <c r="CA13" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="CB13" s="2" t="inlineStr">
+      <c r="CB13" s="2" t="n">
+        <v>1542</v>
+      </c>
+      <c r="CC13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD13" s="2" t="inlineStr">
         <is>
           <t>R2</t>
         </is>
       </c>
-      <c r="CC13" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="CD13" s="2" t="b">
-        <v>0</v>
-      </c>
       <c r="CE13" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CF13" s="2" t="b">
         <v>0</v>
@@ -21714,12 +22140,18 @@
       <c r="CG13" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="CH13" s="2" t="inlineStr">
+      <c r="CH13" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="CI13" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="CJ13" s="2" t="inlineStr">
         <is>
           <t>family_days</t>
         </is>
       </c>
-      <c r="CI13" s="2" t="inlineStr">
+      <c r="CK13" s="2" t="inlineStr">
         <is>
           <t>family_days</t>
         </is>
@@ -21989,33 +22421,33 @@
         <v>0</v>
       </c>
       <c r="BW14" s="2" t="n">
+        <v>1542</v>
+      </c>
+      <c r="BX14" s="2" t="n">
         <v>131</v>
       </c>
-      <c r="BX14" s="2" t="n">
+      <c r="BY14" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="BY14" s="2" t="n">
+      <c r="BZ14" s="2" t="n">
         <v>0.07142857142857142</v>
       </c>
-      <c r="BZ14" s="2" t="n">
+      <c r="CA14" s="2" t="n">
         <v>1675</v>
       </c>
-      <c r="CA14" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="CB14" s="2" t="inlineStr">
+      <c r="CB14" s="2" t="n">
+        <v>1542</v>
+      </c>
+      <c r="CC14" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD14" s="2" t="inlineStr">
         <is>
           <t>R2</t>
         </is>
       </c>
-      <c r="CC14" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="CD14" s="2" t="b">
-        <v>0</v>
-      </c>
       <c r="CE14" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CF14" s="2" t="b">
         <v>0</v>
@@ -22023,12 +22455,18 @@
       <c r="CG14" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="CH14" s="2" t="inlineStr">
+      <c r="CH14" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="CI14" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="CJ14" s="2" t="inlineStr">
         <is>
           <t>family_days</t>
         </is>
       </c>
-      <c r="CI14" s="2" t="inlineStr">
+      <c r="CK14" s="2" t="inlineStr">
         <is>
           <t>family_days</t>
         </is>
@@ -22298,33 +22736,33 @@
         <v>0</v>
       </c>
       <c r="BW15" s="2" t="n">
+        <v>1542</v>
+      </c>
+      <c r="BX15" s="2" t="n">
         <v>131</v>
       </c>
-      <c r="BX15" s="2" t="n">
+      <c r="BY15" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="BY15" s="2" t="n">
+      <c r="BZ15" s="2" t="n">
         <v>0.07142857142857142</v>
       </c>
-      <c r="BZ15" s="2" t="n">
+      <c r="CA15" s="2" t="n">
         <v>1675</v>
       </c>
-      <c r="CA15" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="CB15" s="2" t="inlineStr">
+      <c r="CB15" s="2" t="n">
+        <v>1542</v>
+      </c>
+      <c r="CC15" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD15" s="2" t="inlineStr">
         <is>
           <t>R2</t>
         </is>
       </c>
-      <c r="CC15" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="CD15" s="2" t="b">
-        <v>0</v>
-      </c>
       <c r="CE15" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CF15" s="2" t="b">
         <v>0</v>
@@ -22332,19 +22770,25 @@
       <c r="CG15" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="CH15" s="2" t="inlineStr">
+      <c r="CH15" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="CI15" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="CJ15" s="2" t="inlineStr">
         <is>
           <t>family_days</t>
         </is>
       </c>
-      <c r="CI15" s="2" t="inlineStr">
+      <c r="CK15" s="2" t="inlineStr">
         <is>
           <t>family_days</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:CI15"/>
+  <autoFilter ref="A1:CK15"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -22355,7 +22799,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CN43"/>
+  <dimension ref="A1:CP43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -22432,24 +22876,26 @@
     <col width="22" customWidth="1" min="72" max="72"/>
     <col width="23" customWidth="1" min="73" max="73"/>
     <col width="23" customWidth="1" min="74" max="74"/>
-    <col width="11" customWidth="1" min="75" max="75"/>
-    <col width="21" customWidth="1" min="76" max="76"/>
-    <col width="16" customWidth="1" min="77" max="77"/>
-    <col width="21" customWidth="1" min="78" max="78"/>
-    <col width="22" customWidth="1" min="79" max="79"/>
-    <col width="14" customWidth="1" min="80" max="80"/>
-    <col width="16" customWidth="1" min="81" max="81"/>
-    <col width="18" customWidth="1" min="82" max="82"/>
-    <col width="18" customWidth="1" min="83" max="83"/>
-    <col width="17" customWidth="1" min="84" max="84"/>
-    <col width="12" customWidth="1" min="85" max="85"/>
-    <col width="14" customWidth="1" min="86" max="86"/>
-    <col width="16" customWidth="1" min="87" max="87"/>
-    <col width="18" customWidth="1" min="88" max="88"/>
+    <col width="23" customWidth="1" min="75" max="75"/>
+    <col width="11" customWidth="1" min="76" max="76"/>
+    <col width="21" customWidth="1" min="77" max="77"/>
+    <col width="16" customWidth="1" min="78" max="78"/>
+    <col width="21" customWidth="1" min="79" max="79"/>
+    <col width="33" customWidth="1" min="80" max="80"/>
+    <col width="22" customWidth="1" min="81" max="81"/>
+    <col width="14" customWidth="1" min="82" max="82"/>
+    <col width="16" customWidth="1" min="83" max="83"/>
+    <col width="18" customWidth="1" min="84" max="84"/>
+    <col width="18" customWidth="1" min="85" max="85"/>
+    <col width="17" customWidth="1" min="86" max="86"/>
+    <col width="12" customWidth="1" min="87" max="87"/>
+    <col width="14" customWidth="1" min="88" max="88"/>
     <col width="16" customWidth="1" min="89" max="89"/>
-    <col width="15" customWidth="1" min="90" max="90"/>
-    <col width="11" customWidth="1" min="91" max="91"/>
-    <col width="36" customWidth="1" min="92" max="92"/>
+    <col width="18" customWidth="1" min="90" max="90"/>
+    <col width="16" customWidth="1" min="91" max="91"/>
+    <col width="15" customWidth="1" min="92" max="92"/>
+    <col width="11" customWidth="1" min="93" max="93"/>
+    <col width="36" customWidth="1" min="94" max="94"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -22825,90 +23271,100 @@
       </c>
       <c r="BW1" s="1" t="inlineStr">
         <is>
+          <t>limited_support_hours</t>
+        </is>
+      </c>
+      <c r="BX1" s="1" t="inlineStr">
+        <is>
           <t>ood_hours</t>
         </is>
       </c>
-      <c r="BX1" s="1" t="inlineStr">
+      <c r="BY1" s="1" t="inlineStr">
         <is>
           <t>not_evaluable_hours</t>
         </is>
       </c>
-      <c r="BY1" s="1" t="inlineStr">
+      <c r="BZ1" s="1" t="inlineStr">
         <is>
           <t>post_ref_share</t>
         </is>
       </c>
-      <c r="BZ1" s="1" t="inlineStr">
+      <c r="CA1" s="1" t="inlineStr">
         <is>
           <t>coverage_loss_hours</t>
         </is>
       </c>
-      <c r="CA1" s="1" t="inlineStr">
+      <c r="CB1" s="1" t="inlineStr">
+        <is>
+          <t>support_attributable_loss_hours</t>
+        </is>
+      </c>
+      <c r="CC1" s="1" t="inlineStr">
         <is>
           <t>report_coverage_rate</t>
         </is>
       </c>
-      <c r="CB1" s="1" t="inlineStr">
+      <c r="CD1" s="1" t="inlineStr">
         <is>
           <t>regime_label</t>
         </is>
       </c>
-      <c r="CC1" s="1" t="inlineStr">
+      <c r="CE1" s="1" t="inlineStr">
         <is>
           <t>family_days_l3</t>
         </is>
       </c>
-      <c r="CD1" s="1" t="inlineStr">
+      <c r="CF1" s="1" t="inlineStr">
         <is>
           <t>family_months_l3</t>
         </is>
       </c>
-      <c r="CE1" s="1" t="inlineStr">
+      <c r="CG1" s="1" t="inlineStr">
         <is>
           <t>family_stability</t>
         </is>
       </c>
-      <c r="CF1" s="1" t="inlineStr">
+      <c r="CH1" s="1" t="inlineStr">
         <is>
           <t>family_holdouts</t>
         </is>
       </c>
-      <c r="CG1" s="1" t="inlineStr">
+      <c r="CI1" s="1" t="inlineStr">
         <is>
           <t>family_far</t>
         </is>
       </c>
-      <c r="CH1" s="1" t="inlineStr">
+      <c r="CJ1" s="1" t="inlineStr">
         <is>
           <t>node_days_l3</t>
         </is>
       </c>
-      <c r="CI1" s="1" t="inlineStr">
+      <c r="CK1" s="1" t="inlineStr">
         <is>
           <t>node_months_l3</t>
         </is>
       </c>
-      <c r="CJ1" s="1" t="inlineStr">
+      <c r="CL1" s="1" t="inlineStr">
         <is>
           <t>node_coverage_l3</t>
         </is>
       </c>
-      <c r="CK1" s="1" t="inlineStr">
+      <c r="CM1" s="1" t="inlineStr">
         <is>
           <t>node_stability</t>
         </is>
       </c>
-      <c r="CL1" s="1" t="inlineStr">
+      <c r="CN1" s="1" t="inlineStr">
         <is>
           <t>node_holdouts</t>
         </is>
       </c>
-      <c r="CM1" s="1" t="inlineStr">
+      <c r="CO1" s="1" t="inlineStr">
         <is>
           <t>node_far</t>
         </is>
       </c>
-      <c r="CN1" s="1" t="inlineStr">
+      <c r="CP1" s="1" t="inlineStr">
         <is>
           <t>l3_blocker_set</t>
         </is>
@@ -23192,17 +23648,17 @@
       <c r="CA2" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="CB2" s="2" t="inlineStr">
+      <c r="CB2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD2" s="2" t="inlineStr">
         <is>
           <t>R0</t>
         </is>
       </c>
-      <c r="CC2" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="CD2" s="2" t="b">
-        <v>0</v>
-      </c>
       <c r="CE2" s="2" t="b">
         <v>0</v>
       </c>
@@ -23230,7 +23686,13 @@
       <c r="CM2" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="CN2" s="2" t="inlineStr">
+      <c r="CN2" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="CO2" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="CP2" s="2" t="inlineStr">
         <is>
           <t>none</t>
         </is>
@@ -23514,17 +23976,17 @@
       <c r="CA3" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="CB3" s="2" t="inlineStr">
+      <c r="CB3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD3" s="2" t="inlineStr">
         <is>
           <t>R1</t>
         </is>
       </c>
-      <c r="CC3" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="CD3" s="2" t="b">
-        <v>0</v>
-      </c>
       <c r="CE3" s="2" t="b">
         <v>0</v>
       </c>
@@ -23532,13 +23994,13 @@
         <v>0</v>
       </c>
       <c r="CG3" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CH3" s="2" t="b">
         <v>0</v>
       </c>
       <c r="CI3" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CJ3" s="2" t="b">
         <v>0</v>
@@ -23550,9 +24012,15 @@
         <v>0</v>
       </c>
       <c r="CM3" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="CN3" s="2" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="CN3" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="CO3" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="CP3" s="2" t="inlineStr">
         <is>
           <t>family_far|node_far</t>
         </is>
@@ -23836,31 +24304,31 @@
       <c r="CA4" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="CB4" s="2" t="inlineStr">
+      <c r="CB4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD4" s="2" t="inlineStr">
         <is>
           <t>R3</t>
         </is>
       </c>
-      <c r="CC4" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="CD4" s="2" t="b">
-        <v>0</v>
-      </c>
       <c r="CE4" s="2" t="b">
         <v>1</v>
       </c>
       <c r="CF4" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CG4" s="2" t="b">
         <v>1</v>
       </c>
       <c r="CH4" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CI4" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CJ4" s="2" t="b">
         <v>0</v>
@@ -23869,12 +24337,18 @@
         <v>0</v>
       </c>
       <c r="CL4" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CM4" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="CN4" s="2" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="CN4" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="CO4" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="CP4" s="2" t="inlineStr">
         <is>
           <t>family_days_l3|family_stability|family_holdouts|family_far|node_holdouts|node_far</t>
         </is>
@@ -24158,17 +24632,17 @@
       <c r="CA5" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="CB5" s="2" t="inlineStr">
+      <c r="CB5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD5" s="2" t="inlineStr">
         <is>
           <t>R0</t>
         </is>
       </c>
-      <c r="CC5" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="CD5" s="2" t="b">
-        <v>0</v>
-      </c>
       <c r="CE5" s="2" t="b">
         <v>0</v>
       </c>
@@ -24194,9 +24668,15 @@
         <v>0</v>
       </c>
       <c r="CM5" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="CN5" s="2" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="CN5" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="CO5" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="CP5" s="2" t="inlineStr">
         <is>
           <t>node_far</t>
         </is>
@@ -24480,17 +24960,17 @@
       <c r="CA6" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="CB6" s="2" t="inlineStr">
+      <c r="CB6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD6" s="2" t="inlineStr">
         <is>
           <t>R1</t>
         </is>
       </c>
-      <c r="CC6" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="CD6" s="2" t="b">
-        <v>0</v>
-      </c>
       <c r="CE6" s="2" t="b">
         <v>0</v>
       </c>
@@ -24498,13 +24978,13 @@
         <v>0</v>
       </c>
       <c r="CG6" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CH6" s="2" t="b">
         <v>0</v>
       </c>
       <c r="CI6" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CJ6" s="2" t="b">
         <v>0</v>
@@ -24518,7 +24998,13 @@
       <c r="CM6" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="CN6" s="2" t="inlineStr">
+      <c r="CN6" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="CO6" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="CP6" s="2" t="inlineStr">
         <is>
           <t>family_far</t>
         </is>
@@ -24802,45 +25288,51 @@
       <c r="CA7" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="CB7" s="2" t="inlineStr">
+      <c r="CB7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD7" s="2" t="inlineStr">
         <is>
           <t>R3</t>
         </is>
       </c>
-      <c r="CC7" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="CD7" s="2" t="b">
-        <v>0</v>
-      </c>
       <c r="CE7" s="2" t="b">
         <v>1</v>
       </c>
       <c r="CF7" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CG7" s="2" t="b">
         <v>1</v>
       </c>
       <c r="CH7" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CI7" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CJ7" s="2" t="b">
         <v>0</v>
       </c>
       <c r="CK7" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CL7" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CM7" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="CN7" s="2" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="CN7" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="CO7" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="CP7" s="2" t="inlineStr">
         <is>
           <t>family_days_l3|family_stability|family_holdouts|family_far|node_stability|node_holdouts</t>
         </is>
@@ -25124,17 +25616,17 @@
       <c r="CA8" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="CB8" s="2" t="inlineStr">
+      <c r="CB8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD8" s="2" t="inlineStr">
         <is>
           <t>R0</t>
         </is>
       </c>
-      <c r="CC8" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="CD8" s="2" t="b">
-        <v>0</v>
-      </c>
       <c r="CE8" s="2" t="b">
         <v>0</v>
       </c>
@@ -25162,7 +25654,13 @@
       <c r="CM8" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="CN8" s="2" t="inlineStr">
+      <c r="CN8" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="CO8" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="CP8" s="2" t="inlineStr">
         <is>
           <t>none</t>
         </is>
@@ -25446,17 +25944,17 @@
       <c r="CA9" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="CB9" s="2" t="inlineStr">
+      <c r="CB9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD9" s="2" t="inlineStr">
         <is>
           <t>R1</t>
         </is>
       </c>
-      <c r="CC9" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="CD9" s="2" t="b">
-        <v>0</v>
-      </c>
       <c r="CE9" s="2" t="b">
         <v>0</v>
       </c>
@@ -25464,13 +25962,13 @@
         <v>0</v>
       </c>
       <c r="CG9" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CH9" s="2" t="b">
         <v>0</v>
       </c>
       <c r="CI9" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CJ9" s="2" t="b">
         <v>0</v>
@@ -25482,9 +25980,15 @@
         <v>0</v>
       </c>
       <c r="CM9" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="CN9" s="2" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="CN9" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="CO9" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="CP9" s="2" t="inlineStr">
         <is>
           <t>family_far|node_far</t>
         </is>
@@ -25768,31 +26272,31 @@
       <c r="CA10" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="CB10" s="2" t="inlineStr">
+      <c r="CB10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD10" s="2" t="inlineStr">
         <is>
           <t>R3</t>
         </is>
       </c>
-      <c r="CC10" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="CD10" s="2" t="b">
-        <v>0</v>
-      </c>
       <c r="CE10" s="2" t="b">
         <v>1</v>
       </c>
       <c r="CF10" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CG10" s="2" t="b">
         <v>1</v>
       </c>
       <c r="CH10" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CI10" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CJ10" s="2" t="b">
         <v>0</v>
@@ -25801,12 +26305,18 @@
         <v>0</v>
       </c>
       <c r="CL10" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CM10" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="CN10" s="2" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="CN10" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="CO10" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="CP10" s="2" t="inlineStr">
         <is>
           <t>family_days_l3|family_stability|family_holdouts|family_far|node_holdouts|node_far</t>
         </is>
@@ -26090,17 +26600,17 @@
       <c r="CA11" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="CB11" s="2" t="inlineStr">
+      <c r="CB11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD11" s="2" t="inlineStr">
         <is>
           <t>R0</t>
         </is>
       </c>
-      <c r="CC11" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="CD11" s="2" t="b">
-        <v>0</v>
-      </c>
       <c r="CE11" s="2" t="b">
         <v>0</v>
       </c>
@@ -26120,15 +26630,21 @@
         <v>0</v>
       </c>
       <c r="CK11" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CL11" s="2" t="b">
         <v>0</v>
       </c>
       <c r="CM11" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="CN11" s="2" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="CN11" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="CO11" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="CP11" s="2" t="inlineStr">
         <is>
           <t>node_stability</t>
         </is>
@@ -26412,17 +26928,17 @@
       <c r="CA12" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="CB12" s="2" t="inlineStr">
+      <c r="CB12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD12" s="2" t="inlineStr">
         <is>
           <t>R1</t>
         </is>
       </c>
-      <c r="CC12" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="CD12" s="2" t="b">
-        <v>0</v>
-      </c>
       <c r="CE12" s="2" t="b">
         <v>0</v>
       </c>
@@ -26430,19 +26946,19 @@
         <v>0</v>
       </c>
       <c r="CG12" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CH12" s="2" t="b">
         <v>0</v>
       </c>
       <c r="CI12" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CJ12" s="2" t="b">
         <v>0</v>
       </c>
       <c r="CK12" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CL12" s="2" t="b">
         <v>0</v>
@@ -26450,7 +26966,13 @@
       <c r="CM12" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="CN12" s="2" t="inlineStr">
+      <c r="CN12" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="CO12" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="CP12" s="2" t="inlineStr">
         <is>
           <t>family_far|node_stability|node_far</t>
         </is>
@@ -26734,45 +27256,51 @@
       <c r="CA13" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="CB13" s="2" t="inlineStr">
+      <c r="CB13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD13" s="2" t="inlineStr">
         <is>
           <t>R3</t>
         </is>
       </c>
-      <c r="CC13" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="CD13" s="2" t="b">
-        <v>0</v>
-      </c>
       <c r="CE13" s="2" t="b">
         <v>1</v>
       </c>
       <c r="CF13" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CG13" s="2" t="b">
         <v>1</v>
       </c>
       <c r="CH13" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CI13" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CJ13" s="2" t="b">
         <v>0</v>
       </c>
       <c r="CK13" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CL13" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CM13" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="CN13" s="2" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="CN13" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="CO13" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="CP13" s="2" t="inlineStr">
         <is>
           <t>family_days_l3|family_stability|family_holdouts|family_far|node_stability|node_holdouts</t>
         </is>
@@ -27056,17 +27584,17 @@
       <c r="CA14" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="CB14" s="2" t="inlineStr">
+      <c r="CB14" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC14" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD14" s="2" t="inlineStr">
         <is>
           <t>R0</t>
         </is>
       </c>
-      <c r="CC14" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="CD14" s="2" t="b">
-        <v>0</v>
-      </c>
       <c r="CE14" s="2" t="b">
         <v>0</v>
       </c>
@@ -27092,9 +27620,15 @@
         <v>0</v>
       </c>
       <c r="CM14" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="CN14" s="2" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="CN14" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="CO14" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="CP14" s="2" t="inlineStr">
         <is>
           <t>node_far</t>
         </is>
@@ -27378,17 +27912,17 @@
       <c r="CA15" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="CB15" s="2" t="inlineStr">
+      <c r="CB15" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC15" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD15" s="2" t="inlineStr">
         <is>
           <t>R1</t>
         </is>
       </c>
-      <c r="CC15" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="CD15" s="2" t="b">
-        <v>0</v>
-      </c>
       <c r="CE15" s="2" t="b">
         <v>0</v>
       </c>
@@ -27396,13 +27930,13 @@
         <v>0</v>
       </c>
       <c r="CG15" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CH15" s="2" t="b">
         <v>0</v>
       </c>
       <c r="CI15" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CJ15" s="2" t="b">
         <v>0</v>
@@ -27414,9 +27948,15 @@
         <v>0</v>
       </c>
       <c r="CM15" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="CN15" s="2" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="CN15" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="CO15" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="CP15" s="2" t="inlineStr">
         <is>
           <t>family_far|node_far</t>
         </is>
@@ -27700,31 +28240,31 @@
       <c r="CA16" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="CB16" s="2" t="inlineStr">
+      <c r="CB16" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC16" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD16" s="2" t="inlineStr">
         <is>
           <t>R3</t>
         </is>
       </c>
-      <c r="CC16" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="CD16" s="2" t="b">
-        <v>0</v>
-      </c>
       <c r="CE16" s="2" t="b">
         <v>1</v>
       </c>
       <c r="CF16" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CG16" s="2" t="b">
         <v>1</v>
       </c>
       <c r="CH16" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CI16" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CJ16" s="2" t="b">
         <v>0</v>
@@ -27733,12 +28273,18 @@
         <v>0</v>
       </c>
       <c r="CL16" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CM16" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="CN16" s="2" t="inlineStr">
+      <c r="CN16" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="CO16" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="CP16" s="2" t="inlineStr">
         <is>
           <t>family_days_l3|family_stability|family_holdouts|family_far|node_holdouts</t>
         </is>
@@ -28022,17 +28568,17 @@
       <c r="CA17" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="CB17" s="2" t="inlineStr">
+      <c r="CB17" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC17" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD17" s="2" t="inlineStr">
         <is>
           <t>R0</t>
         </is>
       </c>
-      <c r="CC17" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="CD17" s="2" t="b">
-        <v>0</v>
-      </c>
       <c r="CE17" s="2" t="b">
         <v>0</v>
       </c>
@@ -28060,7 +28606,13 @@
       <c r="CM17" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="CN17" s="2" t="inlineStr">
+      <c r="CN17" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="CO17" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="CP17" s="2" t="inlineStr">
         <is>
           <t>none</t>
         </is>
@@ -28344,17 +28896,17 @@
       <c r="CA18" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="CB18" s="2" t="inlineStr">
+      <c r="CB18" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC18" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD18" s="2" t="inlineStr">
         <is>
           <t>R1</t>
         </is>
       </c>
-      <c r="CC18" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="CD18" s="2" t="b">
-        <v>0</v>
-      </c>
       <c r="CE18" s="2" t="b">
         <v>0</v>
       </c>
@@ -28362,13 +28914,13 @@
         <v>0</v>
       </c>
       <c r="CG18" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CH18" s="2" t="b">
         <v>0</v>
       </c>
       <c r="CI18" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CJ18" s="2" t="b">
         <v>0</v>
@@ -28380,9 +28932,15 @@
         <v>0</v>
       </c>
       <c r="CM18" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="CN18" s="2" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="CN18" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="CO18" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="CP18" s="2" t="inlineStr">
         <is>
           <t>family_far|node_far</t>
         </is>
@@ -28666,31 +29224,31 @@
       <c r="CA19" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="CB19" s="2" t="inlineStr">
+      <c r="CB19" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC19" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD19" s="2" t="inlineStr">
         <is>
           <t>R3</t>
         </is>
       </c>
-      <c r="CC19" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="CD19" s="2" t="b">
-        <v>0</v>
-      </c>
       <c r="CE19" s="2" t="b">
         <v>1</v>
       </c>
       <c r="CF19" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CG19" s="2" t="b">
         <v>1</v>
       </c>
       <c r="CH19" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CI19" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CJ19" s="2" t="b">
         <v>0</v>
@@ -28699,12 +29257,18 @@
         <v>0</v>
       </c>
       <c r="CL19" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CM19" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="CN19" s="2" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="CN19" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="CO19" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="CP19" s="2" t="inlineStr">
         <is>
           <t>family_days_l3|family_stability|family_holdouts|family_far|node_holdouts|node_far</t>
         </is>
@@ -28988,17 +29552,17 @@
       <c r="CA20" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="CB20" s="2" t="inlineStr">
+      <c r="CB20" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC20" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD20" s="2" t="inlineStr">
         <is>
           <t>R0</t>
         </is>
       </c>
-      <c r="CC20" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="CD20" s="2" t="b">
-        <v>0</v>
-      </c>
       <c r="CE20" s="2" t="b">
         <v>0</v>
       </c>
@@ -29024,9 +29588,15 @@
         <v>0</v>
       </c>
       <c r="CM20" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="CN20" s="2" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="CN20" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="CO20" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="CP20" s="2" t="inlineStr">
         <is>
           <t>node_far</t>
         </is>
@@ -29310,17 +29880,17 @@
       <c r="CA21" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="CB21" s="2" t="inlineStr">
+      <c r="CB21" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC21" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD21" s="2" t="inlineStr">
         <is>
           <t>R1</t>
         </is>
       </c>
-      <c r="CC21" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="CD21" s="2" t="b">
-        <v>0</v>
-      </c>
       <c r="CE21" s="2" t="b">
         <v>0</v>
       </c>
@@ -29328,13 +29898,13 @@
         <v>0</v>
       </c>
       <c r="CG21" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CH21" s="2" t="b">
         <v>0</v>
       </c>
       <c r="CI21" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CJ21" s="2" t="b">
         <v>0</v>
@@ -29346,9 +29916,15 @@
         <v>0</v>
       </c>
       <c r="CM21" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="CN21" s="2" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="CN21" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="CO21" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="CP21" s="2" t="inlineStr">
         <is>
           <t>family_far|node_far</t>
         </is>
@@ -29632,31 +30208,31 @@
       <c r="CA22" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="CB22" s="2" t="inlineStr">
+      <c r="CB22" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC22" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD22" s="2" t="inlineStr">
         <is>
           <t>R3</t>
         </is>
       </c>
-      <c r="CC22" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="CD22" s="2" t="b">
-        <v>0</v>
-      </c>
       <c r="CE22" s="2" t="b">
         <v>1</v>
       </c>
       <c r="CF22" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CG22" s="2" t="b">
         <v>1</v>
       </c>
       <c r="CH22" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CI22" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CJ22" s="2" t="b">
         <v>0</v>
@@ -29665,12 +30241,18 @@
         <v>0</v>
       </c>
       <c r="CL22" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CM22" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="CN22" s="2" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="CN22" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="CO22" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="CP22" s="2" t="inlineStr">
         <is>
           <t>family_days_l3|family_stability|family_holdouts|family_far|node_holdouts|node_far</t>
         </is>
@@ -29954,17 +30536,17 @@
       <c r="CA23" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="CB23" s="2" t="inlineStr">
+      <c r="CB23" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC23" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD23" s="2" t="inlineStr">
         <is>
           <t>R0</t>
         </is>
       </c>
-      <c r="CC23" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="CD23" s="2" t="b">
-        <v>0</v>
-      </c>
       <c r="CE23" s="2" t="b">
         <v>0</v>
       </c>
@@ -29990,9 +30572,15 @@
         <v>0</v>
       </c>
       <c r="CM23" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="CN23" s="2" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="CN23" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="CO23" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="CP23" s="2" t="inlineStr">
         <is>
           <t>node_far</t>
         </is>
@@ -30276,17 +30864,17 @@
       <c r="CA24" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="CB24" s="2" t="inlineStr">
+      <c r="CB24" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC24" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD24" s="2" t="inlineStr">
         <is>
           <t>R1</t>
         </is>
       </c>
-      <c r="CC24" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="CD24" s="2" t="b">
-        <v>0</v>
-      </c>
       <c r="CE24" s="2" t="b">
         <v>0</v>
       </c>
@@ -30294,13 +30882,13 @@
         <v>0</v>
       </c>
       <c r="CG24" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CH24" s="2" t="b">
         <v>0</v>
       </c>
       <c r="CI24" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CJ24" s="2" t="b">
         <v>0</v>
@@ -30312,9 +30900,15 @@
         <v>0</v>
       </c>
       <c r="CM24" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="CN24" s="2" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="CN24" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="CO24" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="CP24" s="2" t="inlineStr">
         <is>
           <t>family_far|node_far</t>
         </is>
@@ -30598,45 +31192,51 @@
       <c r="CA25" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="CB25" s="2" t="inlineStr">
+      <c r="CB25" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC25" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD25" s="2" t="inlineStr">
         <is>
           <t>R3</t>
         </is>
       </c>
-      <c r="CC25" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="CD25" s="2" t="b">
-        <v>0</v>
-      </c>
       <c r="CE25" s="2" t="b">
         <v>1</v>
       </c>
       <c r="CF25" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CG25" s="2" t="b">
         <v>1</v>
       </c>
       <c r="CH25" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CI25" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CJ25" s="2" t="b">
         <v>0</v>
       </c>
       <c r="CK25" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CL25" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CM25" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="CN25" s="2" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="CN25" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="CO25" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="CP25" s="2" t="inlineStr">
         <is>
           <t>family_days_l3|family_stability|family_holdouts|family_far|node_stability|node_holdouts</t>
         </is>
@@ -30920,17 +31520,17 @@
       <c r="CA26" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="CB26" s="2" t="inlineStr">
+      <c r="CB26" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC26" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD26" s="2" t="inlineStr">
         <is>
           <t>R0</t>
         </is>
       </c>
-      <c r="CC26" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="CD26" s="2" t="b">
-        <v>0</v>
-      </c>
       <c r="CE26" s="2" t="b">
         <v>0</v>
       </c>
@@ -30938,13 +31538,13 @@
         <v>0</v>
       </c>
       <c r="CG26" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CH26" s="2" t="b">
         <v>0</v>
       </c>
       <c r="CI26" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CJ26" s="2" t="b">
         <v>0</v>
@@ -30956,9 +31556,15 @@
         <v>0</v>
       </c>
       <c r="CM26" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="CN26" s="2" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="CN26" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="CO26" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="CP26" s="2" t="inlineStr">
         <is>
           <t>family_far|node_far</t>
         </is>
@@ -31242,17 +31848,17 @@
       <c r="CA27" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="CB27" s="2" t="inlineStr">
+      <c r="CB27" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC27" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD27" s="2" t="inlineStr">
         <is>
           <t>R1</t>
         </is>
       </c>
-      <c r="CC27" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="CD27" s="2" t="b">
-        <v>0</v>
-      </c>
       <c r="CE27" s="2" t="b">
         <v>0</v>
       </c>
@@ -31260,13 +31866,13 @@
         <v>0</v>
       </c>
       <c r="CG27" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CH27" s="2" t="b">
         <v>0</v>
       </c>
       <c r="CI27" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CJ27" s="2" t="b">
         <v>0</v>
@@ -31278,9 +31884,15 @@
         <v>0</v>
       </c>
       <c r="CM27" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="CN27" s="2" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="CN27" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="CO27" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="CP27" s="2" t="inlineStr">
         <is>
           <t>family_far|node_far</t>
         </is>
@@ -31564,31 +32176,31 @@
       <c r="CA28" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="CB28" s="2" t="inlineStr">
+      <c r="CB28" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC28" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD28" s="2" t="inlineStr">
         <is>
           <t>R3</t>
         </is>
       </c>
-      <c r="CC28" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="CD28" s="2" t="b">
-        <v>0</v>
-      </c>
       <c r="CE28" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CF28" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CG28" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CH28" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CI28" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CJ28" s="2" t="b">
         <v>0</v>
@@ -31597,12 +32209,18 @@
         <v>0</v>
       </c>
       <c r="CL28" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CM28" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="CN28" s="2" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="CN28" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="CO28" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="CP28" s="2" t="inlineStr">
         <is>
           <t>family_days_l3|family_holdouts|family_far|node_holdouts|node_far</t>
         </is>
@@ -31886,17 +32504,17 @@
       <c r="CA29" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="CB29" s="2" t="inlineStr">
+      <c r="CB29" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC29" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD29" s="2" t="inlineStr">
         <is>
           <t>R0</t>
         </is>
       </c>
-      <c r="CC29" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="CD29" s="2" t="b">
-        <v>0</v>
-      </c>
       <c r="CE29" s="2" t="b">
         <v>0</v>
       </c>
@@ -31904,13 +32522,13 @@
         <v>0</v>
       </c>
       <c r="CG29" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CH29" s="2" t="b">
         <v>0</v>
       </c>
       <c r="CI29" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CJ29" s="2" t="b">
         <v>0</v>
@@ -31922,9 +32540,15 @@
         <v>0</v>
       </c>
       <c r="CM29" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="CN29" s="2" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="CN29" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="CO29" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="CP29" s="2" t="inlineStr">
         <is>
           <t>family_far|node_far</t>
         </is>
@@ -32208,17 +32832,17 @@
       <c r="CA30" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="CB30" s="2" t="inlineStr">
+      <c r="CB30" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC30" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD30" s="2" t="inlineStr">
         <is>
           <t>R1</t>
         </is>
       </c>
-      <c r="CC30" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="CD30" s="2" t="b">
-        <v>0</v>
-      </c>
       <c r="CE30" s="2" t="b">
         <v>0</v>
       </c>
@@ -32226,13 +32850,13 @@
         <v>0</v>
       </c>
       <c r="CG30" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CH30" s="2" t="b">
         <v>0</v>
       </c>
       <c r="CI30" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CJ30" s="2" t="b">
         <v>0</v>
@@ -32246,7 +32870,13 @@
       <c r="CM30" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="CN30" s="2" t="inlineStr">
+      <c r="CN30" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="CO30" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="CP30" s="2" t="inlineStr">
         <is>
           <t>family_far</t>
         </is>
@@ -32530,31 +33160,31 @@
       <c r="CA31" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="CB31" s="2" t="inlineStr">
+      <c r="CB31" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC31" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD31" s="2" t="inlineStr">
         <is>
           <t>R3</t>
         </is>
       </c>
-      <c r="CC31" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="CD31" s="2" t="b">
-        <v>0</v>
-      </c>
       <c r="CE31" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CF31" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CG31" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CH31" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CI31" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CJ31" s="2" t="b">
         <v>0</v>
@@ -32563,12 +33193,18 @@
         <v>0</v>
       </c>
       <c r="CL31" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CM31" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="CN31" s="2" t="inlineStr">
+      <c r="CN31" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="CO31" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="CP31" s="2" t="inlineStr">
         <is>
           <t>family_days_l3|family_holdouts|family_far|node_holdouts</t>
         </is>
@@ -32852,17 +33488,17 @@
       <c r="CA32" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="CB32" s="2" t="inlineStr">
+      <c r="CB32" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC32" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD32" s="2" t="inlineStr">
         <is>
           <t>R0</t>
         </is>
       </c>
-      <c r="CC32" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="CD32" s="2" t="b">
-        <v>0</v>
-      </c>
       <c r="CE32" s="2" t="b">
         <v>0</v>
       </c>
@@ -32870,13 +33506,13 @@
         <v>0</v>
       </c>
       <c r="CG32" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CH32" s="2" t="b">
         <v>0</v>
       </c>
       <c r="CI32" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CJ32" s="2" t="b">
         <v>0</v>
@@ -32890,7 +33526,13 @@
       <c r="CM32" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="CN32" s="2" t="inlineStr">
+      <c r="CN32" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="CO32" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="CP32" s="2" t="inlineStr">
         <is>
           <t>family_far</t>
         </is>
@@ -33174,17 +33816,17 @@
       <c r="CA33" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="CB33" s="2" t="inlineStr">
+      <c r="CB33" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC33" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD33" s="2" t="inlineStr">
         <is>
           <t>R1</t>
         </is>
       </c>
-      <c r="CC33" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="CD33" s="2" t="b">
-        <v>0</v>
-      </c>
       <c r="CE33" s="2" t="b">
         <v>0</v>
       </c>
@@ -33192,13 +33834,13 @@
         <v>0</v>
       </c>
       <c r="CG33" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CH33" s="2" t="b">
         <v>0</v>
       </c>
       <c r="CI33" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CJ33" s="2" t="b">
         <v>0</v>
@@ -33210,9 +33852,15 @@
         <v>0</v>
       </c>
       <c r="CM33" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="CN33" s="2" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="CN33" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="CO33" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="CP33" s="2" t="inlineStr">
         <is>
           <t>family_far|node_far</t>
         </is>
@@ -33496,45 +34144,51 @@
       <c r="CA34" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="CB34" s="2" t="inlineStr">
+      <c r="CB34" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC34" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD34" s="2" t="inlineStr">
         <is>
           <t>R3</t>
         </is>
       </c>
-      <c r="CC34" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="CD34" s="2" t="b">
-        <v>0</v>
-      </c>
       <c r="CE34" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CF34" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CG34" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CH34" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CI34" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CJ34" s="2" t="b">
         <v>0</v>
       </c>
       <c r="CK34" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CL34" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CM34" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="CN34" s="2" t="inlineStr">
+      <c r="CN34" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="CO34" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="CP34" s="2" t="inlineStr">
         <is>
           <t>family_days_l3|family_holdouts|family_far|node_stability|node_holdouts|node_far</t>
         </is>
@@ -33818,17 +34472,17 @@
       <c r="CA35" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="CB35" s="2" t="inlineStr">
+      <c r="CB35" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC35" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD35" s="2" t="inlineStr">
         <is>
           <t>R0</t>
         </is>
       </c>
-      <c r="CC35" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="CD35" s="2" t="b">
-        <v>0</v>
-      </c>
       <c r="CE35" s="2" t="b">
         <v>0</v>
       </c>
@@ -33836,13 +34490,13 @@
         <v>0</v>
       </c>
       <c r="CG35" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CH35" s="2" t="b">
         <v>0</v>
       </c>
       <c r="CI35" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CJ35" s="2" t="b">
         <v>0</v>
@@ -33854,9 +34508,15 @@
         <v>0</v>
       </c>
       <c r="CM35" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="CN35" s="2" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="CN35" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="CO35" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="CP35" s="2" t="inlineStr">
         <is>
           <t>family_far|node_far</t>
         </is>
@@ -34140,17 +34800,17 @@
       <c r="CA36" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="CB36" s="2" t="inlineStr">
+      <c r="CB36" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC36" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD36" s="2" t="inlineStr">
         <is>
           <t>R1</t>
         </is>
       </c>
-      <c r="CC36" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="CD36" s="2" t="b">
-        <v>0</v>
-      </c>
       <c r="CE36" s="2" t="b">
         <v>0</v>
       </c>
@@ -34158,19 +34818,19 @@
         <v>0</v>
       </c>
       <c r="CG36" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CH36" s="2" t="b">
         <v>0</v>
       </c>
       <c r="CI36" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CJ36" s="2" t="b">
         <v>0</v>
       </c>
       <c r="CK36" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CL36" s="2" t="b">
         <v>0</v>
@@ -34178,7 +34838,13 @@
       <c r="CM36" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="CN36" s="2" t="inlineStr">
+      <c r="CN36" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="CO36" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="CP36" s="2" t="inlineStr">
         <is>
           <t>family_far|node_stability|node_far</t>
         </is>
@@ -34462,31 +35128,31 @@
       <c r="CA37" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="CB37" s="2" t="inlineStr">
+      <c r="CB37" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC37" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD37" s="2" t="inlineStr">
         <is>
           <t>R3</t>
         </is>
       </c>
-      <c r="CC37" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="CD37" s="2" t="b">
-        <v>0</v>
-      </c>
       <c r="CE37" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CF37" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CG37" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CH37" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CI37" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CJ37" s="2" t="b">
         <v>0</v>
@@ -34495,12 +35161,18 @@
         <v>0</v>
       </c>
       <c r="CL37" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CM37" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="CN37" s="2" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="CN37" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="CO37" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="CP37" s="2" t="inlineStr">
         <is>
           <t>family_days_l3|family_holdouts|family_far|node_holdouts|node_far</t>
         </is>
@@ -34784,17 +35456,17 @@
       <c r="CA38" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="CB38" s="2" t="inlineStr">
+      <c r="CB38" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC38" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD38" s="2" t="inlineStr">
         <is>
           <t>R0</t>
         </is>
       </c>
-      <c r="CC38" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="CD38" s="2" t="b">
-        <v>0</v>
-      </c>
       <c r="CE38" s="2" t="b">
         <v>0</v>
       </c>
@@ -34802,13 +35474,13 @@
         <v>0</v>
       </c>
       <c r="CG38" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CH38" s="2" t="b">
         <v>0</v>
       </c>
       <c r="CI38" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CJ38" s="2" t="b">
         <v>0</v>
@@ -34820,9 +35492,15 @@
         <v>0</v>
       </c>
       <c r="CM38" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="CN38" s="2" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="CN38" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="CO38" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="CP38" s="2" t="inlineStr">
         <is>
           <t>family_far|node_far</t>
         </is>
@@ -35106,17 +35784,17 @@
       <c r="CA39" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="CB39" s="2" t="inlineStr">
+      <c r="CB39" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC39" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD39" s="2" t="inlineStr">
         <is>
           <t>R1</t>
         </is>
       </c>
-      <c r="CC39" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="CD39" s="2" t="b">
-        <v>0</v>
-      </c>
       <c r="CE39" s="2" t="b">
         <v>0</v>
       </c>
@@ -35124,13 +35802,13 @@
         <v>0</v>
       </c>
       <c r="CG39" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CH39" s="2" t="b">
         <v>0</v>
       </c>
       <c r="CI39" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CJ39" s="2" t="b">
         <v>0</v>
@@ -35142,9 +35820,15 @@
         <v>0</v>
       </c>
       <c r="CM39" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="CN39" s="2" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="CN39" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="CO39" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="CP39" s="2" t="inlineStr">
         <is>
           <t>family_far|node_far</t>
         </is>
@@ -35428,31 +36112,31 @@
       <c r="CA40" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="CB40" s="2" t="inlineStr">
+      <c r="CB40" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC40" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD40" s="2" t="inlineStr">
         <is>
           <t>R3</t>
         </is>
       </c>
-      <c r="CC40" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="CD40" s="2" t="b">
-        <v>0</v>
-      </c>
       <c r="CE40" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CF40" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CG40" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CH40" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CI40" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CJ40" s="2" t="b">
         <v>0</v>
@@ -35461,12 +36145,18 @@
         <v>0</v>
       </c>
       <c r="CL40" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CM40" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="CN40" s="2" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="CN40" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="CO40" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="CP40" s="2" t="inlineStr">
         <is>
           <t>family_days_l3|family_holdouts|family_far|node_holdouts|node_far</t>
         </is>
@@ -35750,17 +36440,17 @@
       <c r="CA41" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="CB41" s="2" t="inlineStr">
+      <c r="CB41" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC41" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD41" s="2" t="inlineStr">
         <is>
           <t>R0</t>
         </is>
       </c>
-      <c r="CC41" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="CD41" s="2" t="b">
-        <v>0</v>
-      </c>
       <c r="CE41" s="2" t="b">
         <v>0</v>
       </c>
@@ -35768,13 +36458,13 @@
         <v>0</v>
       </c>
       <c r="CG41" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CH41" s="2" t="b">
         <v>0</v>
       </c>
       <c r="CI41" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CJ41" s="2" t="b">
         <v>0</v>
@@ -35786,9 +36476,15 @@
         <v>0</v>
       </c>
       <c r="CM41" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="CN41" s="2" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="CN41" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="CO41" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="CP41" s="2" t="inlineStr">
         <is>
           <t>family_far|node_far</t>
         </is>
@@ -36072,17 +36768,17 @@
       <c r="CA42" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="CB42" s="2" t="inlineStr">
+      <c r="CB42" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC42" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD42" s="2" t="inlineStr">
         <is>
           <t>R1</t>
         </is>
       </c>
-      <c r="CC42" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="CD42" s="2" t="b">
-        <v>0</v>
-      </c>
       <c r="CE42" s="2" t="b">
         <v>0</v>
       </c>
@@ -36090,13 +36786,13 @@
         <v>0</v>
       </c>
       <c r="CG42" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CH42" s="2" t="b">
         <v>0</v>
       </c>
       <c r="CI42" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CJ42" s="2" t="b">
         <v>0</v>
@@ -36108,9 +36804,15 @@
         <v>0</v>
       </c>
       <c r="CM42" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="CN42" s="2" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="CN42" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="CO42" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="CP42" s="2" t="inlineStr">
         <is>
           <t>family_far|node_far</t>
         </is>
@@ -36394,52 +37096,58 @@
       <c r="CA43" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="CB43" s="2" t="inlineStr">
+      <c r="CB43" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC43" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD43" s="2" t="inlineStr">
         <is>
           <t>R3</t>
         </is>
       </c>
-      <c r="CC43" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="CD43" s="2" t="b">
-        <v>0</v>
-      </c>
       <c r="CE43" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CF43" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CG43" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CH43" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CI43" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CJ43" s="2" t="b">
         <v>0</v>
       </c>
       <c r="CK43" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CL43" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CM43" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="CN43" s="2" t="inlineStr">
+      <c r="CN43" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="CO43" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="CP43" s="2" t="inlineStr">
         <is>
           <t>family_days_l3|family_holdouts|family_far|node_stability|node_holdouts|node_far</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:CN43"/>
+  <autoFilter ref="A1:CP43"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -36450,75 +37158,159 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:H4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="13" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="19" customWidth="1" min="4" max="4"/>
-    <col width="23" customWidth="1" min="5" max="5"/>
-    <col width="36" customWidth="1" min="6" max="6"/>
+    <col width="17" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="19" customWidth="1" min="5" max="5"/>
+    <col width="23" customWidth="1" min="6" max="6"/>
+    <col width="36" customWidth="1" min="7" max="7"/>
+    <col width="30" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>loss_class</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
           <t>primary_blocker</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>blocker_set</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>template_count</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>loss_sensor_hours</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>occupied_sensor_hours</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>coverage_percentage_point_contribution</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>loss_share_within_unreported</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
+          <t>limited_support</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
           <t>family_days</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t>family_days</t>
         </is>
       </c>
-      <c r="C2" s="2" t="n">
+      <c r="D2" s="2" t="n">
         <v>14</v>
       </c>
-      <c r="D2" s="2" t="n">
+      <c r="E2" s="2" t="n">
+        <v>21588</v>
+      </c>
+      <c r="F2" s="2" t="n">
         <v>23450</v>
       </c>
-      <c r="E2" s="2" t="n">
-        <v>23450</v>
-      </c>
-      <c r="F2" s="2" t="n">
-        <v>100</v>
+      <c r="G2" s="2" t="n">
+        <v>92.05970149253731</v>
+      </c>
+      <c r="H2" s="2" t="n">
+        <v>0.9205970149253732</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>out_of_template</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>OOD / out of frozen template</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>1834</v>
+      </c>
+      <c r="F3" s="2" t="n">
+        <v>1834</v>
+      </c>
+      <c r="G3" s="2" t="n">
+        <v>7.82089552238806</v>
+      </c>
+      <c r="H3" s="2" t="n">
+        <v>0.07820895522388059</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>not_evaluable</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Incomplete evidence</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="F4" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="G4" s="2" t="n">
+        <v>0.1194029850746269</v>
+      </c>
+      <c r="H4" s="2" t="n">
+        <v>0.001194029850746269</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F2"/>
+  <autoFilter ref="A1:H4"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -36711,17 +37503,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H13"/>
+  <dimension ref="A1:I13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
     <col width="21" customWidth="1" min="2" max="2"/>
     <col width="11" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="24" customWidth="1" min="5" max="5"/>
+    <col width="36" customWidth="1" min="5" max="5"/>
     <col width="17" customWidth="1" min="6" max="6"/>
-    <col width="32" customWidth="1" min="7" max="7"/>
-    <col width="36" customWidth="1" min="8" max="8"/>
+    <col width="34" customWidth="1" min="7" max="7"/>
+    <col width="32" customWidth="1" min="8" max="8"/>
+    <col width="36" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -36747,7 +37540,7 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>occupied_calendar_days</t>
+          <t>occupied_calendar_days_upper_bound</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -36757,10 +37550,15 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>family_L2_support_horizon_pass</t>
+          <t>family_L2_occupancy_horizon_pass</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>effective_support_recalculated</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>scope</t>
         </is>
@@ -36790,9 +37588,12 @@
       <c r="G2" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>descriptive_support_horizon_with_frozen_K4_assignments</t>
+      <c r="H2" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>descriptive_occupied_day_upper_bound_with_frozen_K4_assignments</t>
         </is>
       </c>
     </row>
@@ -36820,9 +37621,12 @@
       <c r="G3" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>descriptive_support_horizon_with_frozen_K4_assignments</t>
+      <c r="H3" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>descriptive_occupied_day_upper_bound_with_frozen_K4_assignments</t>
         </is>
       </c>
     </row>
@@ -36850,9 +37654,12 @@
       <c r="G4" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>descriptive_support_horizon_with_frozen_K4_assignments</t>
+      <c r="H4" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>descriptive_occupied_day_upper_bound_with_frozen_K4_assignments</t>
         </is>
       </c>
     </row>
@@ -36880,9 +37687,12 @@
       <c r="G5" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>descriptive_support_horizon_with_frozen_K4_assignments</t>
+      <c r="H5" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>descriptive_occupied_day_upper_bound_with_frozen_K4_assignments</t>
         </is>
       </c>
     </row>
@@ -36910,9 +37720,12 @@
       <c r="G6" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>descriptive_support_horizon_with_frozen_K4_assignments</t>
+      <c r="H6" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>descriptive_occupied_day_upper_bound_with_frozen_K4_assignments</t>
         </is>
       </c>
     </row>
@@ -36940,9 +37753,12 @@
       <c r="G7" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>descriptive_support_horizon_with_frozen_K4_assignments</t>
+      <c r="H7" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>descriptive_occupied_day_upper_bound_with_frozen_K4_assignments</t>
         </is>
       </c>
     </row>
@@ -36970,9 +37786,12 @@
       <c r="G8" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>descriptive_support_horizon_with_frozen_K4_assignments</t>
+      <c r="H8" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>descriptive_occupied_day_upper_bound_with_frozen_K4_assignments</t>
         </is>
       </c>
     </row>
@@ -37000,9 +37819,12 @@
       <c r="G9" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>descriptive_support_horizon_with_frozen_K4_assignments</t>
+      <c r="H9" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>descriptive_occupied_day_upper_bound_with_frozen_K4_assignments</t>
         </is>
       </c>
     </row>
@@ -37030,9 +37852,12 @@
       <c r="G10" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>descriptive_support_horizon_with_frozen_K4_assignments</t>
+      <c r="H10" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>descriptive_occupied_day_upper_bound_with_frozen_K4_assignments</t>
         </is>
       </c>
     </row>
@@ -37060,9 +37885,12 @@
       <c r="G11" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>descriptive_support_horizon_with_frozen_K4_assignments</t>
+      <c r="H11" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>descriptive_occupied_day_upper_bound_with_frozen_K4_assignments</t>
         </is>
       </c>
     </row>
@@ -37090,9 +37918,12 @@
       <c r="G12" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>descriptive_support_horizon_with_frozen_K4_assignments</t>
+      <c r="H12" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>descriptive_occupied_day_upper_bound_with_frozen_K4_assignments</t>
         </is>
       </c>
     </row>
@@ -37120,14 +37951,17 @@
       <c r="G13" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>descriptive_support_horizon_with_frozen_K4_assignments</t>
+      <c r="H13" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>descriptive_occupied_day_upper_bound_with_frozen_K4_assignments</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H13"/>
+  <autoFilter ref="A1:I13"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
